--- a/output/pdf_financials_xlsx/ID.xlsx
+++ b/output/pdf_financials_xlsx/ID.xlsx
@@ -5598,37 +5598,37 @@
         <v>0</v>
       </c>
       <c r="G92" s="3" t="n">
-        <v>0</v>
+        <v>0.1936</v>
       </c>
       <c r="H92" s="3" t="n">
-        <v>0</v>
+        <v>1.139798</v>
       </c>
       <c r="I92" s="3" t="n">
-        <v>0</v>
+        <v>1.192697</v>
       </c>
       <c r="J92" s="3" t="n">
-        <v>0</v>
+        <v>1.364585</v>
       </c>
       <c r="K92" s="3" t="n">
-        <v>0</v>
+        <v>1.39042</v>
       </c>
       <c r="L92" s="3" t="n">
-        <v>0</v>
+        <v>1.395096</v>
       </c>
       <c r="M92" s="3" t="n">
-        <v>0</v>
+        <v>1.766815</v>
       </c>
       <c r="N92" s="3" t="n">
-        <v>0</v>
+        <v>1.771534</v>
       </c>
       <c r="O92" s="3" t="n">
-        <v>0</v>
+        <v>1.771534</v>
       </c>
       <c r="P92" s="3" t="n">
-        <v>0</v>
+        <v>1.771534</v>
       </c>
       <c r="Q92" s="3" t="n">
-        <v>0</v>
+        <v>1.815589</v>
       </c>
     </row>
     <row r="93">
@@ -9176,7 +9176,11 @@
           <t>Share-based payment reserve (Note 9)</t>
         </is>
       </c>
-      <c r="D13" t="inlineStr"/>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E13" t="inlineStr">
         <is>
           <t>-</t>
@@ -9270,7 +9274,11 @@
           <t>Warrants reserve</t>
         </is>
       </c>
-      <c r="D14" t="inlineStr"/>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E14" t="inlineStr">
         <is>
           <t>-</t>
@@ -10056,7 +10064,11 @@
           <t>Share-based payment reserve (Note 10)</t>
         </is>
       </c>
-      <c r="D23" t="inlineStr"/>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E23" t="inlineStr">
         <is>
           <t>-</t>
@@ -10608,7 +10620,11 @@
           <t>Warrants reserve (Note 10)</t>
         </is>
       </c>
-      <c r="D29" t="inlineStr"/>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E29" t="inlineStr">
         <is>
           <t>-</t>
@@ -12494,7 +12510,11 @@
           <t>Share-based payment reserve (Note 9)</t>
         </is>
       </c>
-      <c r="D49" t="inlineStr"/>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E49" t="inlineStr">
         <is>
           <t>-</t>
@@ -12588,7 +12608,11 @@
           <t>Warrants reserve (Note 9)</t>
         </is>
       </c>
-      <c r="D50" t="inlineStr"/>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E50" t="inlineStr">
         <is>
           <t>-</t>
@@ -13714,7 +13738,11 @@
           <t>Share-based payment reserve</t>
         </is>
       </c>
-      <c r="D62" t="inlineStr"/>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E62" t="inlineStr">
         <is>
           <t>-</t>
@@ -13808,7 +13836,11 @@
           <t>Warrant reserve</t>
         </is>
       </c>
-      <c r="D63" t="inlineStr"/>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E63" t="inlineStr">
         <is>
           <t>-</t>
@@ -14290,7 +14322,11 @@
           <t>Share-based payment reserve</t>
         </is>
       </c>
-      <c r="D68" t="inlineStr"/>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E68" t="inlineStr">
         <is>
           <t>-</t>
@@ -14384,7 +14420,11 @@
           <t>Warrant reserve</t>
         </is>
       </c>
-      <c r="D69" t="inlineStr"/>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E69" t="inlineStr">
         <is>
           <t>-</t>

--- a/output/pdf_financials_xlsx/ID.xlsx
+++ b/output/pdf_financials_xlsx/ID.xlsx
@@ -2315,13 +2315,13 @@
         </is>
       </c>
       <c r="B34" s="3" t="n">
-        <v>0</v>
+        <v>1.4e-05</v>
       </c>
       <c r="C34" s="3" t="n">
-        <v>0</v>
+        <v>0.000126</v>
       </c>
       <c r="D34" s="3" t="n">
-        <v>0</v>
+        <v>0.000657</v>
       </c>
       <c r="E34" s="3" t="n">
         <v>0</v>
@@ -2330,37 +2330,37 @@
         <v>0</v>
       </c>
       <c r="G34" s="3" t="n">
-        <v>0</v>
+        <v>0.012375</v>
       </c>
       <c r="H34" s="3" t="n">
-        <v>0</v>
+        <v>0.0217</v>
       </c>
       <c r="I34" s="3" t="n">
-        <v>0</v>
+        <v>0.861025</v>
       </c>
       <c r="J34" s="3" t="n">
-        <v>0</v>
+        <v>0.087385</v>
       </c>
       <c r="K34" s="3" t="n">
-        <v>0</v>
+        <v>0.006125</v>
       </c>
       <c r="L34" s="3" t="n">
-        <v>0</v>
+        <v>0.024858</v>
       </c>
       <c r="M34" s="3" t="n">
-        <v>0</v>
+        <v>0.041595</v>
       </c>
       <c r="N34" s="3" t="n">
-        <v>0</v>
+        <v>0.100957</v>
       </c>
       <c r="O34" s="3" t="n">
-        <v>0</v>
+        <v>0.009932</v>
       </c>
       <c r="P34" s="3" t="n">
-        <v>0</v>
+        <v>0.012074</v>
       </c>
       <c r="Q34" s="3" t="n">
-        <v>0</v>
+        <v>0.011706</v>
       </c>
     </row>
     <row r="35">
@@ -2425,13 +2425,13 @@
         </is>
       </c>
       <c r="B36" s="3" t="n">
-        <v>0</v>
+        <v>1.4e-05</v>
       </c>
       <c r="C36" s="3" t="n">
-        <v>0</v>
+        <v>0.000126</v>
       </c>
       <c r="D36" s="3" t="n">
-        <v>0</v>
+        <v>0.000657</v>
       </c>
       <c r="E36" s="3" t="n">
         <v>0</v>
@@ -2440,37 +2440,37 @@
         <v>0</v>
       </c>
       <c r="G36" s="3" t="n">
-        <v>0</v>
+        <v>0.012375</v>
       </c>
       <c r="H36" s="3" t="n">
-        <v>0</v>
+        <v>0.0217</v>
       </c>
       <c r="I36" s="3" t="n">
-        <v>0</v>
+        <v>0.861025</v>
       </c>
       <c r="J36" s="3" t="n">
-        <v>0</v>
+        <v>0.087385</v>
       </c>
       <c r="K36" s="3" t="n">
-        <v>0</v>
+        <v>0.006125</v>
       </c>
       <c r="L36" s="3" t="n">
-        <v>0</v>
+        <v>0.024858</v>
       </c>
       <c r="M36" s="3" t="n">
-        <v>0</v>
+        <v>0.041595</v>
       </c>
       <c r="N36" s="3" t="n">
-        <v>0</v>
+        <v>0.100957</v>
       </c>
       <c r="O36" s="3" t="n">
-        <v>0</v>
+        <v>0.009932</v>
       </c>
       <c r="P36" s="3" t="n">
-        <v>0</v>
+        <v>0.012074</v>
       </c>
       <c r="Q36" s="3" t="n">
-        <v>0</v>
+        <v>0.011706</v>
       </c>
     </row>
     <row r="37">
@@ -3085,13 +3085,13 @@
         </is>
       </c>
       <c r="B48" s="3" t="n">
-        <v>1.4e-05</v>
+        <v>0</v>
       </c>
       <c r="C48" s="3" t="n">
-        <v>0.000126</v>
+        <v>0</v>
       </c>
       <c r="D48" s="3" t="n">
-        <v>0.000627</v>
+        <v>0</v>
       </c>
       <c r="E48" s="3" t="n">
         <v>0</v>
@@ -3100,37 +3100,37 @@
         <v>0</v>
       </c>
       <c r="G48" s="3" t="n">
-        <v>0.012375</v>
+        <v>0</v>
       </c>
       <c r="H48" s="3" t="n">
-        <v>0.044047</v>
+        <v>0.022347</v>
       </c>
       <c r="I48" s="3" t="n">
-        <v>0.871868</v>
+        <v>0.010843</v>
       </c>
       <c r="J48" s="3" t="n">
-        <v>0.09300799999999999</v>
+        <v>0.005623</v>
       </c>
       <c r="K48" s="3" t="n">
-        <v>0.012883</v>
+        <v>0.006758</v>
       </c>
       <c r="L48" s="3" t="n">
-        <v>0.027239</v>
+        <v>0.002381</v>
       </c>
       <c r="M48" s="3" t="n">
-        <v>0.041726</v>
+        <v>0.000131</v>
       </c>
       <c r="N48" s="3" t="n">
-        <v>0.103488</v>
+        <v>0.002531</v>
       </c>
       <c r="O48" s="3" t="n">
-        <v>0.012463</v>
+        <v>0.002531</v>
       </c>
       <c r="P48" s="3" t="n">
-        <v>0.012074</v>
+        <v>0</v>
       </c>
       <c r="Q48" s="3" t="n">
-        <v>0.011706</v>
+        <v>0</v>
       </c>
     </row>
     <row r="49">
@@ -8232,7 +8232,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E2" s="5" t="n">

--- a/output/pdf_financials_xlsx/ID.xlsx
+++ b/output/pdf_financials_xlsx/ID.xlsx
@@ -4362,16 +4362,16 @@
         <v>0</v>
       </c>
       <c r="K70" s="3" t="n">
-        <v>0</v>
+        <v>0.063112</v>
       </c>
       <c r="L70" s="3" t="n">
-        <v>0</v>
+        <v>0.024028</v>
       </c>
       <c r="M70" s="3" t="n">
-        <v>0</v>
+        <v>0.005235</v>
       </c>
       <c r="N70" s="3" t="n">
-        <v>0</v>
+        <v>0.005571</v>
       </c>
       <c r="O70" s="3" t="n">
         <v>0</v>
@@ -4417,16 +4417,16 @@
         <v>0.343044</v>
       </c>
       <c r="K71" s="3" t="n">
-        <v>0.5189820000000001</v>
+        <v>0.582094</v>
       </c>
       <c r="L71" s="3" t="n">
-        <v>0.480995</v>
+        <v>0.505023</v>
       </c>
       <c r="M71" s="3" t="n">
-        <v>0.791318</v>
+        <v>0.796553</v>
       </c>
       <c r="N71" s="3" t="n">
-        <v>0.345012</v>
+        <v>0.350583</v>
       </c>
       <c r="O71" s="3" t="n">
         <v>0.46847</v>
@@ -4637,10 +4637,10 @@
         <v>0.216321</v>
       </c>
       <c r="K75" s="3" t="n">
-        <v>0.305203</v>
+        <v>0.242091</v>
       </c>
       <c r="L75" s="3" t="n">
-        <v>0.28889</v>
+        <v>0.264862</v>
       </c>
       <c r="M75" s="3" t="n">
         <v>0</v>
@@ -4936,16 +4936,16 @@
         <v>-0.4731680538045832</v>
       </c>
       <c r="K80" s="3" t="n">
-        <v>-0.3506312933406119</v>
+        <v>-0.3932706183756087</v>
       </c>
       <c r="L80" s="3" t="n">
-        <v>-0.2961549331243192</v>
+        <v>-0.3109492880201313</v>
       </c>
       <c r="M80" s="3" t="n">
-        <v>-0.4093223859026225</v>
+        <v>-0.4120302766497055</v>
       </c>
       <c r="N80" s="3" t="n">
-        <v>-0.3743538551680736</v>
+        <v>-0.38039864586272</v>
       </c>
       <c r="O80" s="3" t="n">
         <v>-0.3546422501731689</v>
@@ -6060,28 +6060,28 @@
         <v>-0.318187</v>
       </c>
       <c r="J101" s="3" t="n">
-        <v>-0.32058</v>
+        <v>-0.29685</v>
       </c>
       <c r="K101" s="3" t="n">
-        <v>0.123412</v>
+        <v>0.114293</v>
       </c>
       <c r="L101" s="3" t="n">
-        <v>-0.009013</v>
+        <v>-0.021893</v>
       </c>
       <c r="M101" s="3" t="n">
-        <v>0.009143</v>
+        <v>0.000909</v>
       </c>
       <c r="N101" s="3" t="n">
-        <v>0</v>
+        <v>-0.009108</v>
       </c>
       <c r="O101" s="3" t="n">
-        <v>0</v>
+        <v>-0.007842999999999999</v>
       </c>
       <c r="P101" s="3" t="n">
-        <v>0</v>
+        <v>-0.008002</v>
       </c>
       <c r="Q101" s="3" t="n">
-        <v>0</v>
+        <v>0.09506000000000001</v>
       </c>
     </row>
     <row r="102">
@@ -6648,7 +6648,7 @@
         <v>0</v>
       </c>
       <c r="P111" s="3" t="n">
-        <v>0</v>
+        <v>-0.002924</v>
       </c>
       <c r="Q111" s="3" t="n">
         <v>0</v>
@@ -8015,7 +8015,7 @@
         <v>0</v>
       </c>
       <c r="P134" s="3" t="n">
-        <v>0</v>
+        <v>-0.002924</v>
       </c>
       <c r="Q134" s="3" t="n">
         <v>0</v>
@@ -8084,7 +8084,7 @@
         </is>
       </c>
       <c r="P135" s="3" t="n">
-        <v>-0.055842</v>
+        <v>-0.058766</v>
       </c>
       <c r="Q135" s="1" t="inlineStr">
         <is>
@@ -10436,7 +10436,11 @@
           <t>Lease liabilities (Note 8)</t>
         </is>
       </c>
-      <c r="D27" t="inlineStr"/>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>CurrentCapitalLeaseObligation</t>
+        </is>
+      </c>
       <c r="E27" t="inlineStr">
         <is>
           <t>-</t>
@@ -17890,7 +17894,11 @@
           <t>GST receivable</t>
         </is>
       </c>
-      <c r="D106" t="inlineStr"/>
+      <c r="D106" t="inlineStr">
+        <is>
+          <t>ChangeInReceivables</t>
+        </is>
+      </c>
       <c r="E106" t="inlineStr">
         <is>
           <t>-</t>
@@ -18300,7 +18308,11 @@
           <t>Purchase of equipment</t>
         </is>
       </c>
-      <c r="D111" t="inlineStr"/>
+      <c r="D111" t="inlineStr">
+        <is>
+          <t>PurchaseOfPPE</t>
+        </is>
+      </c>
       <c r="E111" t="inlineStr">
         <is>
           <t>-</t>
@@ -19612,7 +19624,11 @@
           <t>Proceeds from share issuance</t>
         </is>
       </c>
-      <c r="D126" t="inlineStr"/>
+      <c r="D126" t="inlineStr">
+        <is>
+          <t>CommonStockIssuance</t>
+        </is>
+      </c>
       <c r="E126" t="inlineStr">
         <is>
           <t>-</t>
@@ -20548,7 +20564,11 @@
           <t>Reversal of write-down of GST receivable</t>
         </is>
       </c>
-      <c r="D136" t="inlineStr"/>
+      <c r="D136" t="inlineStr">
+        <is>
+          <t>ChangeInReceivables</t>
+        </is>
+      </c>
       <c r="E136" t="inlineStr">
         <is>
           <t>-</t>
@@ -21586,7 +21606,11 @@
           <t>Write-off of GST receivable</t>
         </is>
       </c>
-      <c r="D147" t="inlineStr"/>
+      <c r="D147" t="inlineStr">
+        <is>
+          <t>ChangeInReceivables</t>
+        </is>
+      </c>
       <c r="E147" t="inlineStr">
         <is>
           <t>-</t>
